--- a/erp-server/erp-server-file/src/main/resources/excel/wms/dailyInventory.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/dailyInventory.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <r>
       <rPr>
@@ -96,6 +96,9 @@
     <t>结余库存</t>
   </si>
   <si>
+    <t>审核日期</t>
+  </si>
+  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
@@ -115,6 +118,9 @@
   </si>
   <si>
     <t>{.balanceQty}</t>
+  </si>
+  <si>
+    <t>{.date}</t>
   </si>
 </sst>
 </file>
@@ -1077,8 +1083,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.25" customWidth="1"/>
     <col min="2" max="2" width="28.5" customWidth="1"/>
@@ -1086,10 +1092,11 @@
     <col min="4" max="4" width="19.25" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="21.25" customWidth="1"/>
-    <col min="7" max="7" width="13.625" customWidth="1"/>
+    <col min="7" max="7" width="15.75" customWidth="1"/>
+    <col min="8" max="8" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="17.25" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="17.25" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1111,28 +1118,34 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
